--- a/docs/oc-mensuales/gas-licuado-de-petroleo/oct-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/oct-2026.xlsx
@@ -7424,7 +7424,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -17759,7 +17759,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -44344,7 +44344,7 @@
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">

--- a/docs/oc-mensuales/gas-licuado-de-petroleo/oct-2026.xlsx
+++ b/docs/oc-mensuales/gas-licuado-de-petroleo/oct-2026.xlsx
@@ -30889,7 +30889,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
